--- a/data/trans_dic/P37A$otros-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P37A$otros-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -727,52 +727,52 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,42</t>
+          <t>0,15; 1,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,87</t>
+          <t>0,2; 1,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,03</t>
+          <t>0,37; 2,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,18</t>
+          <t>0,65; 2,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,37</t>
+          <t>0,0; 0,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,57</t>
+          <t>0,0; 0,55</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,38</t>
+          <t>0,35; 1,29</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,64</t>
+          <t>0,52; 1,67</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -862,37 +862,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,51</t>
+          <t>0,0; 0,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,97</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,28</t>
+          <t>0,65; 2,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,85</t>
+          <t>0,0; 0,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,69</t>
+          <t>0,0; 0,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,96</t>
+          <t>0,09; 0,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,37</t>
+          <t>0,92; 2,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,43</t>
+          <t>0,05; 0,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,68</t>
+          <t>0,13; 0,66</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,95</t>
+          <t>0,92; 1,97</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,99</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,0; 0,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,17 +1012,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,16</t>
+          <t>0,59; 2,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,86</t>
+          <t>0,0; 0,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 0,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,05</t>
+          <t>0,75; 2,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,57</t>
+          <t>0,06; 0,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,55</t>
+          <t>0,07; 0,61</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,77</t>
+          <t>0,84; 2,15</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,04</t>
+          <t>0,08; 1,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,16</t>
+          <t>0,2; 1,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,43</t>
+          <t>0,0; 0,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1167,17 +1167,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,76</t>
+          <t>0,0; 0,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,69</t>
+          <t>0,16; 0,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,36</t>
+          <t>0,04; 0,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,72</t>
+          <t>0,08; 0,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,76</t>
+          <t>0,24; 0,78</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1277,27 +1277,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,26</t>
+          <t>0,03; 0,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,22</t>
+          <t>0,0; 0,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,71</t>
+          <t>0,2; 0,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,28</t>
+          <t>0,62; 1,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,3</t>
+          <t>0,03; 0,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,57</t>
+          <t>0,17; 0,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,29</t>
+          <t>0,78; 1,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,23</t>
+          <t>0,06; 0,24</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,2</t>
+          <t>0,05; 0,23</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,52</t>
+          <t>0,22; 0,53</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,18</t>
+          <t>0,77; 1,26</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7736</t>
+          <t>8574</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12840</t>
+          <t>13850</t>
         </is>
       </c>
     </row>
@@ -1655,52 +1655,52 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1023; 9594</t>
+          <t>1025; 10533</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1387; 11867</t>
+          <t>1390; 12733</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4967</t>
+          <t>0; 5937</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 7363</t>
+          <t>0; 6572</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2753; 13661</t>
+          <t>2460; 14488</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3894; 15841</t>
+          <t>4749; 16511</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5122</t>
+          <t>0; 4982</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 8043</t>
+          <t>0; 7675</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4570; 18580</t>
+          <t>4669; 17429</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7057; 22316</t>
+          <t>7430; 23763</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12741</t>
+          <t>13047</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14531</t>
+          <t>14927</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27272</t>
+          <t>27975</t>
         </is>
       </c>
     </row>
@@ -1858,57 +1858,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5199</t>
+          <t>0; 4833</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 9948</t>
+          <t>0; 9104</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5224; 27187</t>
+          <t>6799; 27520</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 8226</t>
+          <t>0; 6609</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 7114</t>
+          <t>0; 7923</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>994; 10013</t>
+          <t>990; 8777</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8915; 22747</t>
+          <t>9871; 24388</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 6609</t>
+          <t>0; 6646</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>960; 8916</t>
+          <t>962; 7405</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2582; 14056</t>
+          <t>2668; 13724</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15908; 41939</t>
+          <t>19612; 41672</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>9685</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8538</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16218</t>
+          <t>21207</t>
         </is>
       </c>
     </row>
@@ -2061,32 +2061,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6692</t>
+          <t>0; 6316</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6299</t>
+          <t>0; 4495</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1050; 8485</t>
+          <t>1047; 8540</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3224; 15205</t>
+          <t>4704; 17717</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5898</t>
+          <t>0; 4930</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6236</t>
+          <t>0; 7175</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2096,27 +2096,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3021; 19167</t>
+          <t>6066; 23783</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>760; 7765</t>
+          <t>767; 7129</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 7313</t>
+          <t>0; 7348</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1050; 8481</t>
+          <t>1050; 9478</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8467; 29065</t>
+          <t>13517; 34652</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8797</t>
+          <t>9002</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5302</t>
+          <t>0; 5322</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2279,17 +2279,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>793; 9708</t>
+          <t>788; 10861</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1672; 10757</t>
+          <t>1977; 11060</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4446</t>
+          <t>0; 4395</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2299,17 +2299,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 7937</t>
+          <t>0; 8001</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1572; 7593</t>
+          <t>1743; 8199</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>867; 7080</t>
+          <t>864; 7835</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2319,12 +2319,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1585; 14324</t>
+          <t>1577; 13221</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4654; 15299</t>
+          <t>4970; 16510</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30299</t>
+          <t>32872</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>34830</t>
+          <t>39162</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>65128</t>
+          <t>72034</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>880; 8415</t>
+          <t>876; 8839</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 7488</t>
+          <t>0; 6756</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6929; 23930</t>
+          <t>6729; 23249</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19346; 44262</t>
+          <t>22044; 47690</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>986; 10156</t>
+          <t>984; 10786</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1951; 11884</t>
+          <t>1950; 11838</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5934; 20233</t>
+          <t>5963; 20430</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>24327; 47813</t>
+          <t>29078; 55356</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3806; 15158</t>
+          <t>3725; 15682</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3000; 14019</t>
+          <t>3192; 15800</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15227; 36172</t>
+          <t>15150; 36591</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>49201; 84626</t>
+          <t>56208; 91698</t>
         </is>
       </c>
     </row>
